--- a/artfynd/A 10430-2026 artfynd.xlsx
+++ b/artfynd/A 10430-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88666673</v>
+        <v>112373082</v>
       </c>
       <c r="B2" t="n">
-        <v>85301</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3739</v>
+        <v>433</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Quél.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svanberga N, Upl</t>
+          <t>Södra Järsö, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>705253.3958579456</v>
+        <v>705168</v>
       </c>
       <c r="R2" t="n">
-        <v>6640536.239576943</v>
+        <v>6640435</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +739,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,53 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Anders Haglund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Anders Haglund, Fingal Gyllang, Maryam Bessouda, Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88668302</v>
+        <v>88666680</v>
       </c>
       <c r="B3" t="n">
-        <v>87960</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>970</v>
+        <v>449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>705255.4844805349</v>
+        <v>705253</v>
       </c>
       <c r="R3" t="n">
-        <v>6640407.461840985</v>
+        <v>6640536</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,22 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -915,49 +877,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88666755</v>
+        <v>88668287</v>
       </c>
       <c r="B4" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -966,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>705258.6572215623</v>
+        <v>705243</v>
       </c>
       <c r="R4" t="n">
-        <v>6640468.560387976</v>
+        <v>6640387</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,22 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +971,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1046,12 +985,7 @@
         <v>88666776</v>
       </c>
       <c r="B5" t="n">
-        <v>87960</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>705206.1684996865</v>
+        <v>705206</v>
       </c>
       <c r="R5" t="n">
-        <v>6640460.115335726</v>
+        <v>6640460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,19 +1061,9 @@
           <t>2020-10-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1179,12 +1103,7 @@
         <v>88668285</v>
       </c>
       <c r="B6" t="n">
-        <v>87960</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>705242.5176357055</v>
+        <v>705243</v>
       </c>
       <c r="R6" t="n">
-        <v>6640386.603744741</v>
+        <v>6640387</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1260,19 +1179,9 @@
           <t>2020-10-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,37 +1213,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88666758</v>
+        <v>88668302</v>
       </c>
       <c r="B7" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>970</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1347,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>705258.6572215623</v>
+        <v>705255</v>
       </c>
       <c r="R7" t="n">
-        <v>6640468.560387976</v>
+        <v>6640407</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1377,22 +1281,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,7 +1307,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1424,37 +1318,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88668287</v>
+        <v>88666653</v>
       </c>
       <c r="B8" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>449</v>
+        <v>1988</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1467,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705242.5176357055</v>
+        <v>705321</v>
       </c>
       <c r="R8" t="n">
-        <v>6640386.603744741</v>
+        <v>6640385</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1497,22 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,7 +1412,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1544,32 +1423,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88666680</v>
+        <v>88668278</v>
       </c>
       <c r="B9" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1587,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705253.3958579456</v>
+        <v>705187</v>
       </c>
       <c r="R9" t="n">
-        <v>6640536.239576943</v>
+        <v>6640392</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1617,22 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1664,15 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88666759</v>
+        <v>112292228</v>
       </c>
       <c r="B10" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>3674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1703,17 +1562,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svanberga N, Upl</t>
+          <t>Södra Järsö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705258.6572215623</v>
+        <v>705168</v>
       </c>
       <c r="R10" t="n">
-        <v>6640468.560387976</v>
+        <v>6640435</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1737,22 +1596,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,26 +1620,1295 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Haglund, Fingal Gyllang, Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>88666673</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87375</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svanberga N, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>705253</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6640536</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Ossian Rydebjörk</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>88666629</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svanberga N, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>705330</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6640307</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>88666755</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svanberga N, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>705259</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6640469</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>88668277</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svanberga N, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>705187</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6640392</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-10-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-10-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112292224</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Södra Järsö, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>705168</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6640435</v>
+      </c>
+      <c r="S15" t="n">
+        <v>16</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Haglund, Fingal Gyllang, Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>88666625</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svanberga N, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>705330</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6640307</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>88666759</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svanberga N, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>705259</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6640469</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>88666758</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svanberga N, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>705259</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6640469</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>88668279</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svanberga N, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>705187</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6640392</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-10-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-10-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>88666642</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svanberga N, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>705327</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6640357</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>112292230</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Södra Järsö, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>705168</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6640435</v>
+      </c>
+      <c r="S21" t="n">
+        <v>16</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Haglund, Fingal Gyllang, Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>112373227</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87297</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svanberga N, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>705188</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6640405</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Haglund, Fingal Gyllang, Maryam Bessouda, Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10430-2026 artfynd.xlsx
+++ b/artfynd/A 10430-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112373082</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666680</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88668287</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666776</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88668285</t>
         </is>
       </c>
     </row>
@@ -1315,6 +1345,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88668302</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666653</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88668278</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112292228</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1740,6 +1790,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666673</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1845,6 +1900,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666629</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666755</t>
         </is>
       </c>
     </row>
@@ -2063,6 +2128,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88668277</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2173,6 +2243,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112292224</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2278,6 +2353,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666625</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2383,6 +2463,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666759</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2488,6 +2573,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666758</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2593,6 +2683,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88668279</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2698,6 +2793,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88666642</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2808,6 +2908,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112292230</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2909,8 +3014,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112373227</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>